--- a/modelo_importacao_clientes.xlsx
+++ b/modelo_importacao_clientes.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORTAR_CLIENTES" sheetId="1" r:id="R4063fc0f6d864bc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXEMPLO_PREENCHIDO" sheetId="2" r:id="R37ccf77f58e143a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUÇÕES" sheetId="3" r:id="R45395146161b4d7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORTAR_CLIENTES" sheetId="1" r:id="R9d5c54ca9ad748bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXEMPLO_PREENCHIDO" sheetId="2" r:id="Rcc10c09aa6414cba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUÇÕES" sheetId="3" r:id="Rf541ee8966b344cd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -455,7 +455,7 @@
         <x:v>Ativo</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="20" customHeight="1">
+    <x:row r="2">
       <x:c r="A2" s="12" t="str"/>
       <x:c r="B2" s="12" t="str"/>
       <x:c r="C2" s="14" t="str"/>
@@ -479,7 +479,7 @@
       <x:c r="U2" s="12" t="str"/>
       <x:c r="V2" s="12" t="str"/>
     </x:row>
-    <x:row r="3" ht="20" customHeight="1">
+    <x:row r="3">
       <x:c r="A3" s="12" t="str"/>
       <x:c r="B3" s="12" t="str"/>
       <x:c r="C3" s="14" t="str"/>
@@ -503,7 +503,7 @@
       <x:c r="U3" s="12" t="str"/>
       <x:c r="V3" s="12" t="str"/>
     </x:row>
-    <x:row r="4" ht="20" customHeight="1">
+    <x:row r="4">
       <x:c r="A4" s="12" t="str"/>
       <x:c r="B4" s="12" t="str"/>
       <x:c r="C4" s="14" t="str"/>
@@ -527,7 +527,7 @@
       <x:c r="U4" s="12" t="str"/>
       <x:c r="V4" s="12" t="str"/>
     </x:row>
-    <x:row r="5" ht="20" customHeight="1">
+    <x:row r="5">
       <x:c r="A5" s="12" t="str"/>
       <x:c r="B5" s="12" t="str"/>
       <x:c r="C5" s="14" t="str"/>
@@ -551,7 +551,7 @@
       <x:c r="U5" s="12" t="str"/>
       <x:c r="V5" s="12" t="str"/>
     </x:row>
-    <x:row r="6" ht="20" customHeight="1">
+    <x:row r="6">
       <x:c r="A6" s="12" t="str"/>
       <x:c r="B6" s="12" t="str"/>
       <x:c r="C6" s="14" t="str"/>
@@ -575,7 +575,7 @@
       <x:c r="U6" s="12" t="str"/>
       <x:c r="V6" s="12" t="str"/>
     </x:row>
-    <x:row r="7" ht="20" customHeight="1">
+    <x:row r="7">
       <x:c r="A7" s="12" t="str"/>
       <x:c r="B7" s="12" t="str"/>
       <x:c r="C7" s="14" t="str"/>
@@ -599,7 +599,7 @@
       <x:c r="U7" s="12" t="str"/>
       <x:c r="V7" s="12" t="str"/>
     </x:row>
-    <x:row r="8" ht="20" customHeight="1">
+    <x:row r="8">
       <x:c r="A8" s="12" t="str"/>
       <x:c r="B8" s="12" t="str"/>
       <x:c r="C8" s="14" t="str"/>
@@ -623,7 +623,7 @@
       <x:c r="U8" s="12" t="str"/>
       <x:c r="V8" s="12" t="str"/>
     </x:row>
-    <x:row r="9" ht="20" customHeight="1">
+    <x:row r="9">
       <x:c r="A9" s="12" t="str"/>
       <x:c r="B9" s="12" t="str"/>
       <x:c r="C9" s="14" t="str"/>
@@ -647,7 +647,7 @@
       <x:c r="U9" s="12" t="str"/>
       <x:c r="V9" s="12" t="str"/>
     </x:row>
-    <x:row r="10" ht="20" customHeight="1">
+    <x:row r="10">
       <x:c r="A10" s="12" t="str"/>
       <x:c r="B10" s="12" t="str"/>
       <x:c r="C10" s="14" t="str"/>
@@ -671,7 +671,7 @@
       <x:c r="U10" s="12" t="str"/>
       <x:c r="V10" s="12" t="str"/>
     </x:row>
-    <x:row r="11" ht="20" customHeight="1">
+    <x:row r="11">
       <x:c r="A11" s="12" t="str"/>
       <x:c r="B11" s="12" t="str"/>
       <x:c r="C11" s="14" t="str"/>
@@ -695,7 +695,7 @@
       <x:c r="U11" s="12" t="str"/>
       <x:c r="V11" s="12" t="str"/>
     </x:row>
-    <x:row r="12" ht="20" customHeight="1">
+    <x:row r="12">
       <x:c r="A12" s="12" t="str"/>
       <x:c r="B12" s="12" t="str"/>
       <x:c r="C12" s="14" t="str"/>
@@ -719,7 +719,7 @@
       <x:c r="U12" s="12" t="str"/>
       <x:c r="V12" s="12" t="str"/>
     </x:row>
-    <x:row r="13" ht="20" customHeight="1">
+    <x:row r="13">
       <x:c r="A13" s="12" t="str"/>
       <x:c r="B13" s="12" t="str"/>
       <x:c r="C13" s="14" t="str"/>
@@ -743,7 +743,7 @@
       <x:c r="U13" s="12" t="str"/>
       <x:c r="V13" s="12" t="str"/>
     </x:row>
-    <x:row r="14" ht="20" customHeight="1">
+    <x:row r="14">
       <x:c r="A14" s="12" t="str"/>
       <x:c r="B14" s="12" t="str"/>
       <x:c r="C14" s="14" t="str"/>
@@ -767,7 +767,7 @@
       <x:c r="U14" s="12" t="str"/>
       <x:c r="V14" s="12" t="str"/>
     </x:row>
-    <x:row r="15" ht="20" customHeight="1">
+    <x:row r="15">
       <x:c r="A15" s="12" t="str"/>
       <x:c r="B15" s="12" t="str"/>
       <x:c r="C15" s="14" t="str"/>
@@ -791,7 +791,7 @@
       <x:c r="U15" s="12" t="str"/>
       <x:c r="V15" s="12" t="str"/>
     </x:row>
-    <x:row r="16" ht="20" customHeight="1">
+    <x:row r="16">
       <x:c r="A16" s="12" t="str"/>
       <x:c r="B16" s="12" t="str"/>
       <x:c r="C16" s="14" t="str"/>
@@ -815,7 +815,7 @@
       <x:c r="U16" s="12" t="str"/>
       <x:c r="V16" s="12" t="str"/>
     </x:row>
-    <x:row r="17" ht="20" customHeight="1">
+    <x:row r="17">
       <x:c r="A17" s="12" t="str"/>
       <x:c r="B17" s="12" t="str"/>
       <x:c r="C17" s="14" t="str"/>
@@ -839,7 +839,7 @@
       <x:c r="U17" s="12" t="str"/>
       <x:c r="V17" s="12" t="str"/>
     </x:row>
-    <x:row r="18" ht="20" customHeight="1">
+    <x:row r="18">
       <x:c r="A18" s="12" t="str"/>
       <x:c r="B18" s="12" t="str"/>
       <x:c r="C18" s="14" t="str"/>
@@ -863,7 +863,7 @@
       <x:c r="U18" s="12" t="str"/>
       <x:c r="V18" s="12" t="str"/>
     </x:row>
-    <x:row r="19" ht="20" customHeight="1">
+    <x:row r="19">
       <x:c r="A19" s="12" t="str"/>
       <x:c r="B19" s="12" t="str"/>
       <x:c r="C19" s="14" t="str"/>
@@ -887,7 +887,7 @@
       <x:c r="U19" s="12" t="str"/>
       <x:c r="V19" s="12" t="str"/>
     </x:row>
-    <x:row r="20" ht="20" customHeight="1">
+    <x:row r="20">
       <x:c r="A20" s="12" t="str"/>
       <x:c r="B20" s="12" t="str"/>
       <x:c r="C20" s="14" t="str"/>
@@ -911,7 +911,7 @@
       <x:c r="U20" s="12" t="str"/>
       <x:c r="V20" s="12" t="str"/>
     </x:row>
-    <x:row r="21" ht="20" customHeight="1">
+    <x:row r="21">
       <x:c r="A21" s="12" t="str"/>
       <x:c r="B21" s="12" t="str"/>
       <x:c r="C21" s="14" t="str"/>
@@ -935,7 +935,7 @@
       <x:c r="U21" s="12" t="str"/>
       <x:c r="V21" s="12" t="str"/>
     </x:row>
-    <x:row r="22" ht="20" customHeight="1">
+    <x:row r="22">
       <x:c r="A22" s="12" t="str"/>
       <x:c r="B22" s="12" t="str"/>
       <x:c r="C22" s="14" t="str"/>
@@ -959,7 +959,7 @@
       <x:c r="U22" s="12" t="str"/>
       <x:c r="V22" s="12" t="str"/>
     </x:row>
-    <x:row r="23" ht="20" customHeight="1">
+    <x:row r="23">
       <x:c r="A23" s="12" t="str"/>
       <x:c r="B23" s="12" t="str"/>
       <x:c r="C23" s="14" t="str"/>
@@ -983,7 +983,7 @@
       <x:c r="U23" s="12" t="str"/>
       <x:c r="V23" s="12" t="str"/>
     </x:row>
-    <x:row r="24" ht="20" customHeight="1">
+    <x:row r="24">
       <x:c r="A24" s="12" t="str"/>
       <x:c r="B24" s="12" t="str"/>
       <x:c r="C24" s="14" t="str"/>
@@ -1007,7 +1007,7 @@
       <x:c r="U24" s="12" t="str"/>
       <x:c r="V24" s="12" t="str"/>
     </x:row>
-    <x:row r="25" ht="20" customHeight="1">
+    <x:row r="25">
       <x:c r="A25" s="12" t="str"/>
       <x:c r="B25" s="12" t="str"/>
       <x:c r="C25" s="14" t="str"/>
@@ -1031,7 +1031,7 @@
       <x:c r="U25" s="12" t="str"/>
       <x:c r="V25" s="12" t="str"/>
     </x:row>
-    <x:row r="26" ht="20" customHeight="1">
+    <x:row r="26">
       <x:c r="A26" s="12" t="str"/>
       <x:c r="B26" s="12" t="str"/>
       <x:c r="C26" s="14" t="str"/>
@@ -1055,7 +1055,7 @@
       <x:c r="U26" s="12" t="str"/>
       <x:c r="V26" s="12" t="str"/>
     </x:row>
-    <x:row r="27" ht="20" customHeight="1">
+    <x:row r="27">
       <x:c r="A27" s="12" t="str"/>
       <x:c r="B27" s="12" t="str"/>
       <x:c r="C27" s="14" t="str"/>
@@ -1079,7 +1079,7 @@
       <x:c r="U27" s="12" t="str"/>
       <x:c r="V27" s="12" t="str"/>
     </x:row>
-    <x:row r="28" ht="20" customHeight="1">
+    <x:row r="28">
       <x:c r="A28" s="12" t="str"/>
       <x:c r="B28" s="12" t="str"/>
       <x:c r="C28" s="14" t="str"/>
@@ -1103,7 +1103,7 @@
       <x:c r="U28" s="12" t="str"/>
       <x:c r="V28" s="12" t="str"/>
     </x:row>
-    <x:row r="29" ht="20" customHeight="1">
+    <x:row r="29">
       <x:c r="A29" s="12" t="str"/>
       <x:c r="B29" s="12" t="str"/>
       <x:c r="C29" s="14" t="str"/>
@@ -1127,7 +1127,7 @@
       <x:c r="U29" s="12" t="str"/>
       <x:c r="V29" s="12" t="str"/>
     </x:row>
-    <x:row r="30" ht="20" customHeight="1">
+    <x:row r="30">
       <x:c r="A30" s="12" t="str"/>
       <x:c r="B30" s="12" t="str"/>
       <x:c r="C30" s="14" t="str"/>
@@ -1151,7 +1151,7 @@
       <x:c r="U30" s="12" t="str"/>
       <x:c r="V30" s="12" t="str"/>
     </x:row>
-    <x:row r="31" ht="20" customHeight="1">
+    <x:row r="31">
       <x:c r="A31" s="12" t="str"/>
       <x:c r="B31" s="12" t="str"/>
       <x:c r="C31" s="14" t="str"/>
@@ -1175,7 +1175,7 @@
       <x:c r="U31" s="12" t="str"/>
       <x:c r="V31" s="12" t="str"/>
     </x:row>
-    <x:row r="32" ht="20" customHeight="1">
+    <x:row r="32">
       <x:c r="A32" s="12" t="str"/>
       <x:c r="B32" s="12" t="str"/>
       <x:c r="C32" s="14" t="str"/>
@@ -1199,7 +1199,7 @@
       <x:c r="U32" s="12" t="str"/>
       <x:c r="V32" s="12" t="str"/>
     </x:row>
-    <x:row r="33" ht="20" customHeight="1">
+    <x:row r="33">
       <x:c r="A33" s="12" t="str"/>
       <x:c r="B33" s="12" t="str"/>
       <x:c r="C33" s="14" t="str"/>
@@ -1223,7 +1223,7 @@
       <x:c r="U33" s="12" t="str"/>
       <x:c r="V33" s="12" t="str"/>
     </x:row>
-    <x:row r="34" ht="20" customHeight="1">
+    <x:row r="34">
       <x:c r="A34" s="12" t="str"/>
       <x:c r="B34" s="12" t="str"/>
       <x:c r="C34" s="14" t="str"/>
@@ -1247,7 +1247,7 @@
       <x:c r="U34" s="12" t="str"/>
       <x:c r="V34" s="12" t="str"/>
     </x:row>
-    <x:row r="35" ht="20" customHeight="1">
+    <x:row r="35">
       <x:c r="A35" s="12" t="str"/>
       <x:c r="B35" s="12" t="str"/>
       <x:c r="C35" s="14" t="str"/>
@@ -1271,7 +1271,7 @@
       <x:c r="U35" s="12" t="str"/>
       <x:c r="V35" s="12" t="str"/>
     </x:row>
-    <x:row r="36" ht="20" customHeight="1">
+    <x:row r="36">
       <x:c r="A36" s="12" t="str"/>
       <x:c r="B36" s="12" t="str"/>
       <x:c r="C36" s="14" t="str"/>
@@ -1295,7 +1295,7 @@
       <x:c r="U36" s="12" t="str"/>
       <x:c r="V36" s="12" t="str"/>
     </x:row>
-    <x:row r="37" ht="20" customHeight="1">
+    <x:row r="37">
       <x:c r="A37" s="12" t="str"/>
       <x:c r="B37" s="12" t="str"/>
       <x:c r="C37" s="14" t="str"/>
@@ -1319,7 +1319,7 @@
       <x:c r="U37" s="12" t="str"/>
       <x:c r="V37" s="12" t="str"/>
     </x:row>
-    <x:row r="38" ht="20" customHeight="1">
+    <x:row r="38">
       <x:c r="A38" s="12" t="str"/>
       <x:c r="B38" s="12" t="str"/>
       <x:c r="C38" s="14" t="str"/>
@@ -1343,7 +1343,7 @@
       <x:c r="U38" s="12" t="str"/>
       <x:c r="V38" s="12" t="str"/>
     </x:row>
-    <x:row r="39" ht="20" customHeight="1">
+    <x:row r="39">
       <x:c r="A39" s="12" t="str"/>
       <x:c r="B39" s="12" t="str"/>
       <x:c r="C39" s="14" t="str"/>
@@ -1367,7 +1367,7 @@
       <x:c r="U39" s="12" t="str"/>
       <x:c r="V39" s="12" t="str"/>
     </x:row>
-    <x:row r="40" ht="20" customHeight="1">
+    <x:row r="40">
       <x:c r="A40" s="12" t="str"/>
       <x:c r="B40" s="12" t="str"/>
       <x:c r="C40" s="14" t="str"/>
@@ -1391,7 +1391,7 @@
       <x:c r="U40" s="12" t="str"/>
       <x:c r="V40" s="12" t="str"/>
     </x:row>
-    <x:row r="41" ht="20" customHeight="1">
+    <x:row r="41">
       <x:c r="A41" s="12" t="str"/>
       <x:c r="B41" s="12" t="str"/>
       <x:c r="C41" s="14" t="str"/>
@@ -1415,7 +1415,7 @@
       <x:c r="U41" s="12" t="str"/>
       <x:c r="V41" s="12" t="str"/>
     </x:row>
-    <x:row r="42" ht="20" customHeight="1">
+    <x:row r="42">
       <x:c r="A42" s="12" t="str"/>
       <x:c r="B42" s="12" t="str"/>
       <x:c r="C42" s="14" t="str"/>
@@ -1439,7 +1439,7 @@
       <x:c r="U42" s="12" t="str"/>
       <x:c r="V42" s="12" t="str"/>
     </x:row>
-    <x:row r="43" ht="20" customHeight="1">
+    <x:row r="43">
       <x:c r="A43" s="12" t="str"/>
       <x:c r="B43" s="12" t="str"/>
       <x:c r="C43" s="14" t="str"/>
@@ -1463,7 +1463,7 @@
       <x:c r="U43" s="12" t="str"/>
       <x:c r="V43" s="12" t="str"/>
     </x:row>
-    <x:row r="44" ht="20" customHeight="1">
+    <x:row r="44">
       <x:c r="A44" s="12" t="str"/>
       <x:c r="B44" s="12" t="str"/>
       <x:c r="C44" s="14" t="str"/>
@@ -1487,7 +1487,7 @@
       <x:c r="U44" s="12" t="str"/>
       <x:c r="V44" s="12" t="str"/>
     </x:row>
-    <x:row r="45" ht="20" customHeight="1">
+    <x:row r="45">
       <x:c r="A45" s="12" t="str"/>
       <x:c r="B45" s="12" t="str"/>
       <x:c r="C45" s="14" t="str"/>
@@ -1511,7 +1511,7 @@
       <x:c r="U45" s="12" t="str"/>
       <x:c r="V45" s="12" t="str"/>
     </x:row>
-    <x:row r="46" ht="20" customHeight="1">
+    <x:row r="46">
       <x:c r="A46" s="12" t="str"/>
       <x:c r="B46" s="12" t="str"/>
       <x:c r="C46" s="14" t="str"/>
@@ -1535,7 +1535,7 @@
       <x:c r="U46" s="12" t="str"/>
       <x:c r="V46" s="12" t="str"/>
     </x:row>
-    <x:row r="47" ht="20" customHeight="1">
+    <x:row r="47">
       <x:c r="A47" s="12" t="str"/>
       <x:c r="B47" s="12" t="str"/>
       <x:c r="C47" s="14" t="str"/>
@@ -1559,7 +1559,7 @@
       <x:c r="U47" s="12" t="str"/>
       <x:c r="V47" s="12" t="str"/>
     </x:row>
-    <x:row r="48" ht="20" customHeight="1">
+    <x:row r="48">
       <x:c r="A48" s="12" t="str"/>
       <x:c r="B48" s="12" t="str"/>
       <x:c r="C48" s="14" t="str"/>
@@ -1583,7 +1583,7 @@
       <x:c r="U48" s="12" t="str"/>
       <x:c r="V48" s="12" t="str"/>
     </x:row>
-    <x:row r="49" ht="20" customHeight="1">
+    <x:row r="49">
       <x:c r="A49" s="12" t="str"/>
       <x:c r="B49" s="12" t="str"/>
       <x:c r="C49" s="14" t="str"/>
@@ -1607,7 +1607,7 @@
       <x:c r="U49" s="12" t="str"/>
       <x:c r="V49" s="12" t="str"/>
     </x:row>
-    <x:row r="50" ht="20" customHeight="1">
+    <x:row r="50">
       <x:c r="A50" s="12" t="str"/>
       <x:c r="B50" s="12" t="str"/>
       <x:c r="C50" s="14" t="str"/>
@@ -1631,7 +1631,7 @@
       <x:c r="U50" s="12" t="str"/>
       <x:c r="V50" s="12" t="str"/>
     </x:row>
-    <x:row r="51" ht="20" customHeight="1">
+    <x:row r="51">
       <x:c r="A51" s="12" t="str"/>
       <x:c r="B51" s="12" t="str"/>
       <x:c r="C51" s="14" t="str"/>
@@ -1655,7 +1655,7 @@
       <x:c r="U51" s="12" t="str"/>
       <x:c r="V51" s="12" t="str"/>
     </x:row>
-    <x:row r="52" ht="20" customHeight="1">
+    <x:row r="52">
       <x:c r="A52" s="12" t="str"/>
       <x:c r="B52" s="12" t="str"/>
       <x:c r="C52" s="14" t="str"/>
@@ -1679,7 +1679,7 @@
       <x:c r="U52" s="12" t="str"/>
       <x:c r="V52" s="12" t="str"/>
     </x:row>
-    <x:row r="53" ht="20" customHeight="1">
+    <x:row r="53">
       <x:c r="A53" s="12" t="str"/>
       <x:c r="B53" s="12" t="str"/>
       <x:c r="C53" s="14" t="str"/>
@@ -1703,7 +1703,7 @@
       <x:c r="U53" s="12" t="str"/>
       <x:c r="V53" s="12" t="str"/>
     </x:row>
-    <x:row r="54" ht="20" customHeight="1">
+    <x:row r="54">
       <x:c r="A54" s="12" t="str"/>
       <x:c r="B54" s="12" t="str"/>
       <x:c r="C54" s="14" t="str"/>
@@ -1727,7 +1727,7 @@
       <x:c r="U54" s="12" t="str"/>
       <x:c r="V54" s="12" t="str"/>
     </x:row>
-    <x:row r="55" ht="20" customHeight="1">
+    <x:row r="55">
       <x:c r="A55" s="12" t="str"/>
       <x:c r="B55" s="12" t="str"/>
       <x:c r="C55" s="14" t="str"/>
@@ -1751,7 +1751,7 @@
       <x:c r="U55" s="12" t="str"/>
       <x:c r="V55" s="12" t="str"/>
     </x:row>
-    <x:row r="56" ht="20" customHeight="1">
+    <x:row r="56">
       <x:c r="A56" s="12" t="str"/>
       <x:c r="B56" s="12" t="str"/>
       <x:c r="C56" s="14" t="str"/>
@@ -1775,7 +1775,7 @@
       <x:c r="U56" s="12" t="str"/>
       <x:c r="V56" s="12" t="str"/>
     </x:row>
-    <x:row r="57" ht="20" customHeight="1">
+    <x:row r="57">
       <x:c r="A57" s="12" t="str"/>
       <x:c r="B57" s="12" t="str"/>
       <x:c r="C57" s="14" t="str"/>
@@ -1799,7 +1799,7 @@
       <x:c r="U57" s="12" t="str"/>
       <x:c r="V57" s="12" t="str"/>
     </x:row>
-    <x:row r="58" ht="20" customHeight="1">
+    <x:row r="58">
       <x:c r="A58" s="12" t="str"/>
       <x:c r="B58" s="12" t="str"/>
       <x:c r="C58" s="14" t="str"/>
@@ -1823,7 +1823,7 @@
       <x:c r="U58" s="12" t="str"/>
       <x:c r="V58" s="12" t="str"/>
     </x:row>
-    <x:row r="59" ht="20" customHeight="1">
+    <x:row r="59">
       <x:c r="A59" s="12" t="str"/>
       <x:c r="B59" s="12" t="str"/>
       <x:c r="C59" s="14" t="str"/>
@@ -1847,7 +1847,7 @@
       <x:c r="U59" s="12" t="str"/>
       <x:c r="V59" s="12" t="str"/>
     </x:row>
-    <x:row r="60" ht="20" customHeight="1">
+    <x:row r="60">
       <x:c r="A60" s="12" t="str"/>
       <x:c r="B60" s="12" t="str"/>
       <x:c r="C60" s="14" t="str"/>
@@ -1871,7 +1871,7 @@
       <x:c r="U60" s="12" t="str"/>
       <x:c r="V60" s="12" t="str"/>
     </x:row>
-    <x:row r="61" ht="20" customHeight="1">
+    <x:row r="61">
       <x:c r="A61" s="12" t="str"/>
       <x:c r="B61" s="12" t="str"/>
       <x:c r="C61" s="14" t="str"/>
@@ -1895,7 +1895,7 @@
       <x:c r="U61" s="12" t="str"/>
       <x:c r="V61" s="12" t="str"/>
     </x:row>
-    <x:row r="62" ht="20" customHeight="1">
+    <x:row r="62">
       <x:c r="A62" s="12" t="str"/>
       <x:c r="B62" s="12" t="str"/>
       <x:c r="C62" s="14" t="str"/>
@@ -1919,7 +1919,7 @@
       <x:c r="U62" s="12" t="str"/>
       <x:c r="V62" s="12" t="str"/>
     </x:row>
-    <x:row r="63" ht="20" customHeight="1">
+    <x:row r="63">
       <x:c r="A63" s="12" t="str"/>
       <x:c r="B63" s="12" t="str"/>
       <x:c r="C63" s="14" t="str"/>
@@ -1943,7 +1943,7 @@
       <x:c r="U63" s="12" t="str"/>
       <x:c r="V63" s="12" t="str"/>
     </x:row>
-    <x:row r="64" ht="20" customHeight="1">
+    <x:row r="64">
       <x:c r="A64" s="12" t="str"/>
       <x:c r="B64" s="12" t="str"/>
       <x:c r="C64" s="14" t="str"/>
@@ -1967,7 +1967,7 @@
       <x:c r="U64" s="12" t="str"/>
       <x:c r="V64" s="12" t="str"/>
     </x:row>
-    <x:row r="65" ht="20" customHeight="1">
+    <x:row r="65">
       <x:c r="A65" s="12" t="str"/>
       <x:c r="B65" s="12" t="str"/>
       <x:c r="C65" s="14" t="str"/>
@@ -1991,7 +1991,7 @@
       <x:c r="U65" s="12" t="str"/>
       <x:c r="V65" s="12" t="str"/>
     </x:row>
-    <x:row r="66" ht="20" customHeight="1">
+    <x:row r="66">
       <x:c r="A66" s="12" t="str"/>
       <x:c r="B66" s="12" t="str"/>
       <x:c r="C66" s="14" t="str"/>
@@ -2015,7 +2015,7 @@
       <x:c r="U66" s="12" t="str"/>
       <x:c r="V66" s="12" t="str"/>
     </x:row>
-    <x:row r="67" ht="20" customHeight="1">
+    <x:row r="67">
       <x:c r="A67" s="12" t="str"/>
       <x:c r="B67" s="12" t="str"/>
       <x:c r="C67" s="14" t="str"/>
@@ -2039,7 +2039,7 @@
       <x:c r="U67" s="12" t="str"/>
       <x:c r="V67" s="12" t="str"/>
     </x:row>
-    <x:row r="68" ht="20" customHeight="1">
+    <x:row r="68">
       <x:c r="A68" s="12" t="str"/>
       <x:c r="B68" s="12" t="str"/>
       <x:c r="C68" s="14" t="str"/>
@@ -2063,7 +2063,7 @@
       <x:c r="U68" s="12" t="str"/>
       <x:c r="V68" s="12" t="str"/>
     </x:row>
-    <x:row r="69" ht="20" customHeight="1">
+    <x:row r="69">
       <x:c r="A69" s="12" t="str"/>
       <x:c r="B69" s="12" t="str"/>
       <x:c r="C69" s="14" t="str"/>
@@ -2087,7 +2087,7 @@
       <x:c r="U69" s="12" t="str"/>
       <x:c r="V69" s="12" t="str"/>
     </x:row>
-    <x:row r="70" ht="20" customHeight="1">
+    <x:row r="70">
       <x:c r="A70" s="12" t="str"/>
       <x:c r="B70" s="12" t="str"/>
       <x:c r="C70" s="14" t="str"/>
@@ -2111,7 +2111,7 @@
       <x:c r="U70" s="12" t="str"/>
       <x:c r="V70" s="12" t="str"/>
     </x:row>
-    <x:row r="71" ht="20" customHeight="1">
+    <x:row r="71">
       <x:c r="A71" s="12" t="str"/>
       <x:c r="B71" s="12" t="str"/>
       <x:c r="C71" s="14" t="str"/>
@@ -2135,7 +2135,7 @@
       <x:c r="U71" s="12" t="str"/>
       <x:c r="V71" s="12" t="str"/>
     </x:row>
-    <x:row r="72" ht="20" customHeight="1">
+    <x:row r="72">
       <x:c r="A72" s="12" t="str"/>
       <x:c r="B72" s="12" t="str"/>
       <x:c r="C72" s="14" t="str"/>
@@ -2159,7 +2159,7 @@
       <x:c r="U72" s="12" t="str"/>
       <x:c r="V72" s="12" t="str"/>
     </x:row>
-    <x:row r="73" ht="20" customHeight="1">
+    <x:row r="73">
       <x:c r="A73" s="12" t="str"/>
       <x:c r="B73" s="12" t="str"/>
       <x:c r="C73" s="14" t="str"/>
@@ -2183,7 +2183,7 @@
       <x:c r="U73" s="12" t="str"/>
       <x:c r="V73" s="12" t="str"/>
     </x:row>
-    <x:row r="74" ht="20" customHeight="1">
+    <x:row r="74">
       <x:c r="A74" s="12" t="str"/>
       <x:c r="B74" s="12" t="str"/>
       <x:c r="C74" s="14" t="str"/>
@@ -2207,7 +2207,7 @@
       <x:c r="U74" s="12" t="str"/>
       <x:c r="V74" s="12" t="str"/>
     </x:row>
-    <x:row r="75" ht="20" customHeight="1">
+    <x:row r="75">
       <x:c r="A75" s="12" t="str"/>
       <x:c r="B75" s="12" t="str"/>
       <x:c r="C75" s="14" t="str"/>
@@ -2231,7 +2231,7 @@
       <x:c r="U75" s="12" t="str"/>
       <x:c r="V75" s="12" t="str"/>
     </x:row>
-    <x:row r="76" ht="20" customHeight="1">
+    <x:row r="76">
       <x:c r="A76" s="12" t="str"/>
       <x:c r="B76" s="12" t="str"/>
       <x:c r="C76" s="14" t="str"/>
@@ -2255,7 +2255,7 @@
       <x:c r="U76" s="12" t="str"/>
       <x:c r="V76" s="12" t="str"/>
     </x:row>
-    <x:row r="77" ht="20" customHeight="1">
+    <x:row r="77">
       <x:c r="A77" s="12" t="str"/>
       <x:c r="B77" s="12" t="str"/>
       <x:c r="C77" s="14" t="str"/>
@@ -2279,7 +2279,7 @@
       <x:c r="U77" s="12" t="str"/>
       <x:c r="V77" s="12" t="str"/>
     </x:row>
-    <x:row r="78" ht="20" customHeight="1">
+    <x:row r="78">
       <x:c r="A78" s="12" t="str"/>
       <x:c r="B78" s="12" t="str"/>
       <x:c r="C78" s="14" t="str"/>
@@ -2303,7 +2303,7 @@
       <x:c r="U78" s="12" t="str"/>
       <x:c r="V78" s="12" t="str"/>
     </x:row>
-    <x:row r="79" ht="20" customHeight="1">
+    <x:row r="79">
       <x:c r="A79" s="12" t="str"/>
       <x:c r="B79" s="12" t="str"/>
       <x:c r="C79" s="14" t="str"/>
@@ -2327,7 +2327,7 @@
       <x:c r="U79" s="12" t="str"/>
       <x:c r="V79" s="12" t="str"/>
     </x:row>
-    <x:row r="80" ht="20" customHeight="1">
+    <x:row r="80">
       <x:c r="A80" s="12" t="str"/>
       <x:c r="B80" s="12" t="str"/>
       <x:c r="C80" s="14" t="str"/>
@@ -2351,7 +2351,7 @@
       <x:c r="U80" s="12" t="str"/>
       <x:c r="V80" s="12" t="str"/>
     </x:row>
-    <x:row r="81" ht="20" customHeight="1">
+    <x:row r="81">
       <x:c r="A81" s="12" t="str"/>
       <x:c r="B81" s="12" t="str"/>
       <x:c r="C81" s="14" t="str"/>
@@ -2375,7 +2375,7 @@
       <x:c r="U81" s="12" t="str"/>
       <x:c r="V81" s="12" t="str"/>
     </x:row>
-    <x:row r="82" ht="20" customHeight="1">
+    <x:row r="82">
       <x:c r="A82" s="12" t="str"/>
       <x:c r="B82" s="12" t="str"/>
       <x:c r="C82" s="14" t="str"/>
@@ -2399,7 +2399,7 @@
       <x:c r="U82" s="12" t="str"/>
       <x:c r="V82" s="12" t="str"/>
     </x:row>
-    <x:row r="83" ht="20" customHeight="1">
+    <x:row r="83">
       <x:c r="A83" s="12" t="str"/>
       <x:c r="B83" s="12" t="str"/>
       <x:c r="C83" s="14" t="str"/>
@@ -2423,7 +2423,7 @@
       <x:c r="U83" s="12" t="str"/>
       <x:c r="V83" s="12" t="str"/>
     </x:row>
-    <x:row r="84" ht="20" customHeight="1">
+    <x:row r="84">
       <x:c r="A84" s="12" t="str"/>
       <x:c r="B84" s="12" t="str"/>
       <x:c r="C84" s="14" t="str"/>
@@ -2447,7 +2447,7 @@
       <x:c r="U84" s="12" t="str"/>
       <x:c r="V84" s="12" t="str"/>
     </x:row>
-    <x:row r="85" ht="20" customHeight="1">
+    <x:row r="85">
       <x:c r="A85" s="12" t="str"/>
       <x:c r="B85" s="12" t="str"/>
       <x:c r="C85" s="14" t="str"/>
@@ -2471,7 +2471,7 @@
       <x:c r="U85" s="12" t="str"/>
       <x:c r="V85" s="12" t="str"/>
     </x:row>
-    <x:row r="86" ht="20" customHeight="1">
+    <x:row r="86">
       <x:c r="A86" s="12" t="str"/>
       <x:c r="B86" s="12" t="str"/>
       <x:c r="C86" s="14" t="str"/>
@@ -2495,7 +2495,7 @@
       <x:c r="U86" s="12" t="str"/>
       <x:c r="V86" s="12" t="str"/>
     </x:row>
-    <x:row r="87" ht="20" customHeight="1">
+    <x:row r="87">
       <x:c r="A87" s="12" t="str"/>
       <x:c r="B87" s="12" t="str"/>
       <x:c r="C87" s="14" t="str"/>
@@ -2519,7 +2519,7 @@
       <x:c r="U87" s="12" t="str"/>
       <x:c r="V87" s="12" t="str"/>
     </x:row>
-    <x:row r="88" ht="20" customHeight="1">
+    <x:row r="88">
       <x:c r="A88" s="12" t="str"/>
       <x:c r="B88" s="12" t="str"/>
       <x:c r="C88" s="14" t="str"/>
@@ -2543,7 +2543,7 @@
       <x:c r="U88" s="12" t="str"/>
       <x:c r="V88" s="12" t="str"/>
     </x:row>
-    <x:row r="89" ht="20" customHeight="1">
+    <x:row r="89">
       <x:c r="A89" s="12" t="str"/>
       <x:c r="B89" s="12" t="str"/>
       <x:c r="C89" s="14" t="str"/>
@@ -2567,7 +2567,7 @@
       <x:c r="U89" s="12" t="str"/>
       <x:c r="V89" s="12" t="str"/>
     </x:row>
-    <x:row r="90" ht="20" customHeight="1">
+    <x:row r="90">
       <x:c r="A90" s="12" t="str"/>
       <x:c r="B90" s="12" t="str"/>
       <x:c r="C90" s="14" t="str"/>
@@ -2591,7 +2591,7 @@
       <x:c r="U90" s="12" t="str"/>
       <x:c r="V90" s="12" t="str"/>
     </x:row>
-    <x:row r="91" ht="20" customHeight="1">
+    <x:row r="91">
       <x:c r="A91" s="12" t="str"/>
       <x:c r="B91" s="12" t="str"/>
       <x:c r="C91" s="14" t="str"/>
@@ -2615,7 +2615,7 @@
       <x:c r="U91" s="12" t="str"/>
       <x:c r="V91" s="12" t="str"/>
     </x:row>
-    <x:row r="92" ht="20" customHeight="1">
+    <x:row r="92">
       <x:c r="A92" s="12" t="str"/>
       <x:c r="B92" s="12" t="str"/>
       <x:c r="C92" s="14" t="str"/>
@@ -2639,7 +2639,7 @@
       <x:c r="U92" s="12" t="str"/>
       <x:c r="V92" s="12" t="str"/>
     </x:row>
-    <x:row r="93" ht="20" customHeight="1">
+    <x:row r="93">
       <x:c r="A93" s="12" t="str"/>
       <x:c r="B93" s="12" t="str"/>
       <x:c r="C93" s="14" t="str"/>
@@ -2663,7 +2663,7 @@
       <x:c r="U93" s="12" t="str"/>
       <x:c r="V93" s="12" t="str"/>
     </x:row>
-    <x:row r="94" ht="20" customHeight="1">
+    <x:row r="94">
       <x:c r="A94" s="12" t="str"/>
       <x:c r="B94" s="12" t="str"/>
       <x:c r="C94" s="14" t="str"/>
@@ -2687,7 +2687,7 @@
       <x:c r="U94" s="12" t="str"/>
       <x:c r="V94" s="12" t="str"/>
     </x:row>
-    <x:row r="95" ht="20" customHeight="1">
+    <x:row r="95">
       <x:c r="A95" s="12" t="str"/>
       <x:c r="B95" s="12" t="str"/>
       <x:c r="C95" s="14" t="str"/>
@@ -2711,7 +2711,7 @@
       <x:c r="U95" s="12" t="str"/>
       <x:c r="V95" s="12" t="str"/>
     </x:row>
-    <x:row r="96" ht="20" customHeight="1">
+    <x:row r="96">
       <x:c r="A96" s="12" t="str"/>
       <x:c r="B96" s="12" t="str"/>
       <x:c r="C96" s="14" t="str"/>
@@ -2735,7 +2735,7 @@
       <x:c r="U96" s="12" t="str"/>
       <x:c r="V96" s="12" t="str"/>
     </x:row>
-    <x:row r="97" ht="20" customHeight="1">
+    <x:row r="97">
       <x:c r="A97" s="12" t="str"/>
       <x:c r="B97" s="12" t="str"/>
       <x:c r="C97" s="14" t="str"/>
@@ -2759,7 +2759,7 @@
       <x:c r="U97" s="12" t="str"/>
       <x:c r="V97" s="12" t="str"/>
     </x:row>
-    <x:row r="98" ht="20" customHeight="1">
+    <x:row r="98">
       <x:c r="A98" s="12" t="str"/>
       <x:c r="B98" s="12" t="str"/>
       <x:c r="C98" s="14" t="str"/>
@@ -2783,7 +2783,7 @@
       <x:c r="U98" s="12" t="str"/>
       <x:c r="V98" s="12" t="str"/>
     </x:row>
-    <x:row r="99" ht="20" customHeight="1">
+    <x:row r="99">
       <x:c r="A99" s="12" t="str"/>
       <x:c r="B99" s="12" t="str"/>
       <x:c r="C99" s="14" t="str"/>
@@ -2807,7 +2807,7 @@
       <x:c r="U99" s="12" t="str"/>
       <x:c r="V99" s="12" t="str"/>
     </x:row>
-    <x:row r="100" ht="20" customHeight="1">
+    <x:row r="100">
       <x:c r="A100" s="12" t="str"/>
       <x:c r="B100" s="12" t="str"/>
       <x:c r="C100" s="14" t="str"/>
@@ -2831,7 +2831,7 @@
       <x:c r="U100" s="12" t="str"/>
       <x:c r="V100" s="12" t="str"/>
     </x:row>
-    <x:row r="101" ht="20" customHeight="1">
+    <x:row r="101">
       <x:c r="A101" s="12" t="str"/>
       <x:c r="B101" s="12" t="str"/>
       <x:c r="C101" s="14" t="str"/>
@@ -2855,7 +2855,7 @@
       <x:c r="U101" s="12" t="str"/>
       <x:c r="V101" s="12" t="str"/>
     </x:row>
-    <x:row r="102" ht="20" customHeight="1">
+    <x:row r="102">
       <x:c r="A102" s="12" t="str"/>
       <x:c r="B102" s="12" t="str"/>
       <x:c r="C102" s="14" t="str"/>
@@ -2879,7 +2879,7 @@
       <x:c r="U102" s="12" t="str"/>
       <x:c r="V102" s="12" t="str"/>
     </x:row>
-    <x:row r="103" ht="20" customHeight="1">
+    <x:row r="103">
       <x:c r="A103" s="12" t="str"/>
       <x:c r="B103" s="12" t="str"/>
       <x:c r="C103" s="14" t="str"/>
@@ -2903,7 +2903,7 @@
       <x:c r="U103" s="12" t="str"/>
       <x:c r="V103" s="12" t="str"/>
     </x:row>
-    <x:row r="104" ht="20" customHeight="1">
+    <x:row r="104">
       <x:c r="A104" s="12" t="str"/>
       <x:c r="B104" s="12" t="str"/>
       <x:c r="C104" s="14" t="str"/>
@@ -2927,7 +2927,7 @@
       <x:c r="U104" s="12" t="str"/>
       <x:c r="V104" s="12" t="str"/>
     </x:row>
-    <x:row r="105" ht="20" customHeight="1">
+    <x:row r="105">
       <x:c r="A105" s="12" t="str"/>
       <x:c r="B105" s="12" t="str"/>
       <x:c r="C105" s="14" t="str"/>
@@ -2951,7 +2951,7 @@
       <x:c r="U105" s="12" t="str"/>
       <x:c r="V105" s="12" t="str"/>
     </x:row>
-    <x:row r="106" ht="20" customHeight="1">
+    <x:row r="106">
       <x:c r="A106" s="12" t="str"/>
       <x:c r="B106" s="12" t="str"/>
       <x:c r="C106" s="14" t="str"/>
@@ -2975,7 +2975,7 @@
       <x:c r="U106" s="12" t="str"/>
       <x:c r="V106" s="12" t="str"/>
     </x:row>
-    <x:row r="107" ht="20" customHeight="1">
+    <x:row r="107">
       <x:c r="A107" s="12" t="str"/>
       <x:c r="B107" s="12" t="str"/>
       <x:c r="C107" s="14" t="str"/>
@@ -2999,7 +2999,7 @@
       <x:c r="U107" s="12" t="str"/>
       <x:c r="V107" s="12" t="str"/>
     </x:row>
-    <x:row r="108" ht="20" customHeight="1">
+    <x:row r="108">
       <x:c r="A108" s="12" t="str"/>
       <x:c r="B108" s="12" t="str"/>
       <x:c r="C108" s="14" t="str"/>
@@ -3023,7 +3023,7 @@
       <x:c r="U108" s="12" t="str"/>
       <x:c r="V108" s="12" t="str"/>
     </x:row>
-    <x:row r="109" ht="20" customHeight="1">
+    <x:row r="109">
       <x:c r="A109" s="12" t="str"/>
       <x:c r="B109" s="12" t="str"/>
       <x:c r="C109" s="14" t="str"/>
@@ -3047,7 +3047,7 @@
       <x:c r="U109" s="12" t="str"/>
       <x:c r="V109" s="12" t="str"/>
     </x:row>
-    <x:row r="110" ht="20" customHeight="1">
+    <x:row r="110">
       <x:c r="A110" s="12" t="str"/>
       <x:c r="B110" s="12" t="str"/>
       <x:c r="C110" s="14" t="str"/>
@@ -3071,7 +3071,7 @@
       <x:c r="U110" s="12" t="str"/>
       <x:c r="V110" s="12" t="str"/>
     </x:row>
-    <x:row r="111" ht="20" customHeight="1">
+    <x:row r="111">
       <x:c r="A111" s="12" t="str"/>
       <x:c r="B111" s="12" t="str"/>
       <x:c r="C111" s="14" t="str"/>
@@ -3095,7 +3095,7 @@
       <x:c r="U111" s="12" t="str"/>
       <x:c r="V111" s="12" t="str"/>
     </x:row>
-    <x:row r="112" ht="20" customHeight="1">
+    <x:row r="112">
       <x:c r="A112" s="12" t="str"/>
       <x:c r="B112" s="12" t="str"/>
       <x:c r="C112" s="14" t="str"/>
@@ -3119,7 +3119,7 @@
       <x:c r="U112" s="12" t="str"/>
       <x:c r="V112" s="12" t="str"/>
     </x:row>
-    <x:row r="113" ht="20" customHeight="1">
+    <x:row r="113">
       <x:c r="A113" s="12" t="str"/>
       <x:c r="B113" s="12" t="str"/>
       <x:c r="C113" s="14" t="str"/>
@@ -3143,7 +3143,7 @@
       <x:c r="U113" s="12" t="str"/>
       <x:c r="V113" s="12" t="str"/>
     </x:row>
-    <x:row r="114" ht="20" customHeight="1">
+    <x:row r="114">
       <x:c r="A114" s="12" t="str"/>
       <x:c r="B114" s="12" t="str"/>
       <x:c r="C114" s="14" t="str"/>
@@ -3167,7 +3167,7 @@
       <x:c r="U114" s="12" t="str"/>
       <x:c r="V114" s="12" t="str"/>
     </x:row>
-    <x:row r="115" ht="20" customHeight="1">
+    <x:row r="115">
       <x:c r="A115" s="12" t="str"/>
       <x:c r="B115" s="12" t="str"/>
       <x:c r="C115" s="14" t="str"/>
@@ -3191,7 +3191,7 @@
       <x:c r="U115" s="12" t="str"/>
       <x:c r="V115" s="12" t="str"/>
     </x:row>
-    <x:row r="116" ht="20" customHeight="1">
+    <x:row r="116">
       <x:c r="A116" s="12" t="str"/>
       <x:c r="B116" s="12" t="str"/>
       <x:c r="C116" s="14" t="str"/>
@@ -3215,7 +3215,7 @@
       <x:c r="U116" s="12" t="str"/>
       <x:c r="V116" s="12" t="str"/>
     </x:row>
-    <x:row r="117" ht="20" customHeight="1">
+    <x:row r="117">
       <x:c r="A117" s="12" t="str"/>
       <x:c r="B117" s="12" t="str"/>
       <x:c r="C117" s="14" t="str"/>
@@ -3239,7 +3239,7 @@
       <x:c r="U117" s="12" t="str"/>
       <x:c r="V117" s="12" t="str"/>
     </x:row>
-    <x:row r="118" ht="20" customHeight="1">
+    <x:row r="118">
       <x:c r="A118" s="12" t="str"/>
       <x:c r="B118" s="12" t="str"/>
       <x:c r="C118" s="14" t="str"/>
@@ -3263,7 +3263,7 @@
       <x:c r="U118" s="12" t="str"/>
       <x:c r="V118" s="12" t="str"/>
     </x:row>
-    <x:row r="119" ht="20" customHeight="1">
+    <x:row r="119">
       <x:c r="A119" s="12" t="str"/>
       <x:c r="B119" s="12" t="str"/>
       <x:c r="C119" s="14" t="str"/>
@@ -3287,7 +3287,7 @@
       <x:c r="U119" s="12" t="str"/>
       <x:c r="V119" s="12" t="str"/>
     </x:row>
-    <x:row r="120" ht="20" customHeight="1">
+    <x:row r="120">
       <x:c r="A120" s="12" t="str"/>
       <x:c r="B120" s="12" t="str"/>
       <x:c r="C120" s="14" t="str"/>
@@ -3311,7 +3311,7 @@
       <x:c r="U120" s="12" t="str"/>
       <x:c r="V120" s="12" t="str"/>
     </x:row>
-    <x:row r="121" ht="20" customHeight="1">
+    <x:row r="121">
       <x:c r="A121" s="12" t="str"/>
       <x:c r="B121" s="12" t="str"/>
       <x:c r="C121" s="14" t="str"/>
@@ -3335,7 +3335,7 @@
       <x:c r="U121" s="12" t="str"/>
       <x:c r="V121" s="12" t="str"/>
     </x:row>
-    <x:row r="122" ht="20" customHeight="1">
+    <x:row r="122">
       <x:c r="A122" s="12" t="str"/>
       <x:c r="B122" s="12" t="str"/>
       <x:c r="C122" s="14" t="str"/>
@@ -3359,7 +3359,7 @@
       <x:c r="U122" s="12" t="str"/>
       <x:c r="V122" s="12" t="str"/>
     </x:row>
-    <x:row r="123" ht="20" customHeight="1">
+    <x:row r="123">
       <x:c r="A123" s="12" t="str"/>
       <x:c r="B123" s="12" t="str"/>
       <x:c r="C123" s="14" t="str"/>
@@ -3383,7 +3383,7 @@
       <x:c r="U123" s="12" t="str"/>
       <x:c r="V123" s="12" t="str"/>
     </x:row>
-    <x:row r="124" ht="20" customHeight="1">
+    <x:row r="124">
       <x:c r="A124" s="12" t="str"/>
       <x:c r="B124" s="12" t="str"/>
       <x:c r="C124" s="14" t="str"/>
@@ -3407,7 +3407,7 @@
       <x:c r="U124" s="12" t="str"/>
       <x:c r="V124" s="12" t="str"/>
     </x:row>
-    <x:row r="125" ht="20" customHeight="1">
+    <x:row r="125">
       <x:c r="A125" s="12" t="str"/>
       <x:c r="B125" s="12" t="str"/>
       <x:c r="C125" s="14" t="str"/>
@@ -3431,7 +3431,7 @@
       <x:c r="U125" s="12" t="str"/>
       <x:c r="V125" s="12" t="str"/>
     </x:row>
-    <x:row r="126" ht="20" customHeight="1">
+    <x:row r="126">
       <x:c r="A126" s="12" t="str"/>
       <x:c r="B126" s="12" t="str"/>
       <x:c r="C126" s="14" t="str"/>
@@ -3455,7 +3455,7 @@
       <x:c r="U126" s="12" t="str"/>
       <x:c r="V126" s="12" t="str"/>
     </x:row>
-    <x:row r="127" ht="20" customHeight="1">
+    <x:row r="127">
       <x:c r="A127" s="12" t="str"/>
       <x:c r="B127" s="12" t="str"/>
       <x:c r="C127" s="14" t="str"/>
@@ -3479,7 +3479,7 @@
       <x:c r="U127" s="12" t="str"/>
       <x:c r="V127" s="12" t="str"/>
     </x:row>
-    <x:row r="128" ht="20" customHeight="1">
+    <x:row r="128">
       <x:c r="A128" s="12" t="str"/>
       <x:c r="B128" s="12" t="str"/>
       <x:c r="C128" s="14" t="str"/>
@@ -3503,7 +3503,7 @@
       <x:c r="U128" s="12" t="str"/>
       <x:c r="V128" s="12" t="str"/>
     </x:row>
-    <x:row r="129" ht="20" customHeight="1">
+    <x:row r="129">
       <x:c r="A129" s="12" t="str"/>
       <x:c r="B129" s="12" t="str"/>
       <x:c r="C129" s="14" t="str"/>
@@ -3527,7 +3527,7 @@
       <x:c r="U129" s="12" t="str"/>
       <x:c r="V129" s="12" t="str"/>
     </x:row>
-    <x:row r="130" ht="20" customHeight="1">
+    <x:row r="130">
       <x:c r="A130" s="12" t="str"/>
       <x:c r="B130" s="12" t="str"/>
       <x:c r="C130" s="14" t="str"/>
@@ -3551,7 +3551,7 @@
       <x:c r="U130" s="12" t="str"/>
       <x:c r="V130" s="12" t="str"/>
     </x:row>
-    <x:row r="131" ht="20" customHeight="1">
+    <x:row r="131">
       <x:c r="A131" s="12" t="str"/>
       <x:c r="B131" s="12" t="str"/>
       <x:c r="C131" s="14" t="str"/>
@@ -3575,7 +3575,7 @@
       <x:c r="U131" s="12" t="str"/>
       <x:c r="V131" s="12" t="str"/>
     </x:row>
-    <x:row r="132" ht="20" customHeight="1">
+    <x:row r="132">
       <x:c r="A132" s="12" t="str"/>
       <x:c r="B132" s="12" t="str"/>
       <x:c r="C132" s="14" t="str"/>
@@ -3599,7 +3599,7 @@
       <x:c r="U132" s="12" t="str"/>
       <x:c r="V132" s="12" t="str"/>
     </x:row>
-    <x:row r="133" ht="20" customHeight="1">
+    <x:row r="133">
       <x:c r="A133" s="12" t="str"/>
       <x:c r="B133" s="12" t="str"/>
       <x:c r="C133" s="14" t="str"/>
@@ -3623,7 +3623,7 @@
       <x:c r="U133" s="12" t="str"/>
       <x:c r="V133" s="12" t="str"/>
     </x:row>
-    <x:row r="134" ht="20" customHeight="1">
+    <x:row r="134">
       <x:c r="A134" s="12" t="str"/>
       <x:c r="B134" s="12" t="str"/>
       <x:c r="C134" s="14" t="str"/>
@@ -3647,7 +3647,7 @@
       <x:c r="U134" s="12" t="str"/>
       <x:c r="V134" s="12" t="str"/>
     </x:row>
-    <x:row r="135" ht="20" customHeight="1">
+    <x:row r="135">
       <x:c r="A135" s="12" t="str"/>
       <x:c r="B135" s="12" t="str"/>
       <x:c r="C135" s="14" t="str"/>
@@ -3671,7 +3671,7 @@
       <x:c r="U135" s="12" t="str"/>
       <x:c r="V135" s="12" t="str"/>
     </x:row>
-    <x:row r="136" ht="20" customHeight="1">
+    <x:row r="136">
       <x:c r="A136" s="12" t="str"/>
       <x:c r="B136" s="12" t="str"/>
       <x:c r="C136" s="14" t="str"/>
@@ -3695,7 +3695,7 @@
       <x:c r="U136" s="12" t="str"/>
       <x:c r="V136" s="12" t="str"/>
     </x:row>
-    <x:row r="137" ht="20" customHeight="1">
+    <x:row r="137">
       <x:c r="A137" s="12" t="str"/>
       <x:c r="B137" s="12" t="str"/>
       <x:c r="C137" s="14" t="str"/>
@@ -3719,7 +3719,7 @@
       <x:c r="U137" s="12" t="str"/>
       <x:c r="V137" s="12" t="str"/>
     </x:row>
-    <x:row r="138" ht="20" customHeight="1">
+    <x:row r="138">
       <x:c r="A138" s="12" t="str"/>
       <x:c r="B138" s="12" t="str"/>
       <x:c r="C138" s="14" t="str"/>
@@ -3743,7 +3743,7 @@
       <x:c r="U138" s="12" t="str"/>
       <x:c r="V138" s="12" t="str"/>
     </x:row>
-    <x:row r="139" ht="20" customHeight="1">
+    <x:row r="139">
       <x:c r="A139" s="12" t="str"/>
       <x:c r="B139" s="12" t="str"/>
       <x:c r="C139" s="14" t="str"/>
@@ -3767,7 +3767,7 @@
       <x:c r="U139" s="12" t="str"/>
       <x:c r="V139" s="12" t="str"/>
     </x:row>
-    <x:row r="140" ht="20" customHeight="1">
+    <x:row r="140">
       <x:c r="A140" s="12" t="str"/>
       <x:c r="B140" s="12" t="str"/>
       <x:c r="C140" s="14" t="str"/>
@@ -3791,7 +3791,7 @@
       <x:c r="U140" s="12" t="str"/>
       <x:c r="V140" s="12" t="str"/>
     </x:row>
-    <x:row r="141" ht="20" customHeight="1">
+    <x:row r="141">
       <x:c r="A141" s="12" t="str"/>
       <x:c r="B141" s="12" t="str"/>
       <x:c r="C141" s="14" t="str"/>
@@ -3815,7 +3815,7 @@
       <x:c r="U141" s="12" t="str"/>
       <x:c r="V141" s="12" t="str"/>
     </x:row>
-    <x:row r="142" ht="20" customHeight="1">
+    <x:row r="142">
       <x:c r="A142" s="12" t="str"/>
       <x:c r="B142" s="12" t="str"/>
       <x:c r="C142" s="14" t="str"/>
@@ -3839,7 +3839,7 @@
       <x:c r="U142" s="12" t="str"/>
       <x:c r="V142" s="12" t="str"/>
     </x:row>
-    <x:row r="143" ht="20" customHeight="1">
+    <x:row r="143">
       <x:c r="A143" s="12" t="str"/>
       <x:c r="B143" s="12" t="str"/>
       <x:c r="C143" s="14" t="str"/>
@@ -3863,7 +3863,7 @@
       <x:c r="U143" s="12" t="str"/>
       <x:c r="V143" s="12" t="str"/>
     </x:row>
-    <x:row r="144" ht="20" customHeight="1">
+    <x:row r="144">
       <x:c r="A144" s="12" t="str"/>
       <x:c r="B144" s="12" t="str"/>
       <x:c r="C144" s="14" t="str"/>
@@ -3887,7 +3887,7 @@
       <x:c r="U144" s="12" t="str"/>
       <x:c r="V144" s="12" t="str"/>
     </x:row>
-    <x:row r="145" ht="20" customHeight="1">
+    <x:row r="145">
       <x:c r="A145" s="12" t="str"/>
       <x:c r="B145" s="12" t="str"/>
       <x:c r="C145" s="14" t="str"/>
@@ -3911,7 +3911,7 @@
       <x:c r="U145" s="12" t="str"/>
       <x:c r="V145" s="12" t="str"/>
     </x:row>
-    <x:row r="146" ht="20" customHeight="1">
+    <x:row r="146">
       <x:c r="A146" s="12" t="str"/>
       <x:c r="B146" s="12" t="str"/>
       <x:c r="C146" s="14" t="str"/>
@@ -3935,7 +3935,7 @@
       <x:c r="U146" s="12" t="str"/>
       <x:c r="V146" s="12" t="str"/>
     </x:row>
-    <x:row r="147" ht="20" customHeight="1">
+    <x:row r="147">
       <x:c r="A147" s="12" t="str"/>
       <x:c r="B147" s="12" t="str"/>
       <x:c r="C147" s="14" t="str"/>
@@ -3959,7 +3959,7 @@
       <x:c r="U147" s="12" t="str"/>
       <x:c r="V147" s="12" t="str"/>
     </x:row>
-    <x:row r="148" ht="20" customHeight="1">
+    <x:row r="148">
       <x:c r="A148" s="12" t="str"/>
       <x:c r="B148" s="12" t="str"/>
       <x:c r="C148" s="14" t="str"/>
@@ -3983,7 +3983,7 @@
       <x:c r="U148" s="12" t="str"/>
       <x:c r="V148" s="12" t="str"/>
     </x:row>
-    <x:row r="149" ht="20" customHeight="1">
+    <x:row r="149">
       <x:c r="A149" s="12" t="str"/>
       <x:c r="B149" s="12" t="str"/>
       <x:c r="C149" s="14" t="str"/>
@@ -4007,7 +4007,7 @@
       <x:c r="U149" s="12" t="str"/>
       <x:c r="V149" s="12" t="str"/>
     </x:row>
-    <x:row r="150" ht="20" customHeight="1">
+    <x:row r="150">
       <x:c r="A150" s="12" t="str"/>
       <x:c r="B150" s="12" t="str"/>
       <x:c r="C150" s="14" t="str"/>
@@ -4031,7 +4031,7 @@
       <x:c r="U150" s="12" t="str"/>
       <x:c r="V150" s="12" t="str"/>
     </x:row>
-    <x:row r="151" ht="20" customHeight="1">
+    <x:row r="151">
       <x:c r="A151" s="12" t="str"/>
       <x:c r="B151" s="12" t="str"/>
       <x:c r="C151" s="14" t="str"/>
@@ -4055,7 +4055,7 @@
       <x:c r="U151" s="12" t="str"/>
       <x:c r="V151" s="12" t="str"/>
     </x:row>
-    <x:row r="152" ht="20" customHeight="1">
+    <x:row r="152">
       <x:c r="A152" s="12" t="str"/>
       <x:c r="B152" s="12" t="str"/>
       <x:c r="C152" s="14" t="str"/>
@@ -4079,7 +4079,7 @@
       <x:c r="U152" s="12" t="str"/>
       <x:c r="V152" s="12" t="str"/>
     </x:row>
-    <x:row r="153" ht="20" customHeight="1">
+    <x:row r="153">
       <x:c r="A153" s="12" t="str"/>
       <x:c r="B153" s="12" t="str"/>
       <x:c r="C153" s="14" t="str"/>
@@ -4103,7 +4103,7 @@
       <x:c r="U153" s="12" t="str"/>
       <x:c r="V153" s="12" t="str"/>
     </x:row>
-    <x:row r="154" ht="20" customHeight="1">
+    <x:row r="154">
       <x:c r="A154" s="12" t="str"/>
       <x:c r="B154" s="12" t="str"/>
       <x:c r="C154" s="14" t="str"/>
@@ -4127,7 +4127,7 @@
       <x:c r="U154" s="12" t="str"/>
       <x:c r="V154" s="12" t="str"/>
     </x:row>
-    <x:row r="155" ht="20" customHeight="1">
+    <x:row r="155">
       <x:c r="A155" s="12" t="str"/>
       <x:c r="B155" s="12" t="str"/>
       <x:c r="C155" s="14" t="str"/>
@@ -4151,7 +4151,7 @@
       <x:c r="U155" s="12" t="str"/>
       <x:c r="V155" s="12" t="str"/>
     </x:row>
-    <x:row r="156" ht="20" customHeight="1">
+    <x:row r="156">
       <x:c r="A156" s="12" t="str"/>
       <x:c r="B156" s="12" t="str"/>
       <x:c r="C156" s="14" t="str"/>
@@ -4175,7 +4175,7 @@
       <x:c r="U156" s="12" t="str"/>
       <x:c r="V156" s="12" t="str"/>
     </x:row>
-    <x:row r="157" ht="20" customHeight="1">
+    <x:row r="157">
       <x:c r="A157" s="12" t="str"/>
       <x:c r="B157" s="12" t="str"/>
       <x:c r="C157" s="14" t="str"/>
@@ -4199,7 +4199,7 @@
       <x:c r="U157" s="12" t="str"/>
       <x:c r="V157" s="12" t="str"/>
     </x:row>
-    <x:row r="158" ht="20" customHeight="1">
+    <x:row r="158">
       <x:c r="A158" s="12" t="str"/>
       <x:c r="B158" s="12" t="str"/>
       <x:c r="C158" s="14" t="str"/>
@@ -4223,7 +4223,7 @@
       <x:c r="U158" s="12" t="str"/>
       <x:c r="V158" s="12" t="str"/>
     </x:row>
-    <x:row r="159" ht="20" customHeight="1">
+    <x:row r="159">
       <x:c r="A159" s="12" t="str"/>
       <x:c r="B159" s="12" t="str"/>
       <x:c r="C159" s="14" t="str"/>
@@ -4247,7 +4247,7 @@
       <x:c r="U159" s="12" t="str"/>
       <x:c r="V159" s="12" t="str"/>
     </x:row>
-    <x:row r="160" ht="20" customHeight="1">
+    <x:row r="160">
       <x:c r="A160" s="12" t="str"/>
       <x:c r="B160" s="12" t="str"/>
       <x:c r="C160" s="14" t="str"/>
@@ -4271,7 +4271,7 @@
       <x:c r="U160" s="12" t="str"/>
       <x:c r="V160" s="12" t="str"/>
     </x:row>
-    <x:row r="161" ht="20" customHeight="1">
+    <x:row r="161">
       <x:c r="A161" s="12" t="str"/>
       <x:c r="B161" s="12" t="str"/>
       <x:c r="C161" s="14" t="str"/>
@@ -4295,7 +4295,7 @@
       <x:c r="U161" s="12" t="str"/>
       <x:c r="V161" s="12" t="str"/>
     </x:row>
-    <x:row r="162" ht="20" customHeight="1">
+    <x:row r="162">
       <x:c r="A162" s="12" t="str"/>
       <x:c r="B162" s="12" t="str"/>
       <x:c r="C162" s="14" t="str"/>
@@ -4319,7 +4319,7 @@
       <x:c r="U162" s="12" t="str"/>
       <x:c r="V162" s="12" t="str"/>
     </x:row>
-    <x:row r="163" ht="20" customHeight="1">
+    <x:row r="163">
       <x:c r="A163" s="12" t="str"/>
       <x:c r="B163" s="12" t="str"/>
       <x:c r="C163" s="14" t="str"/>
@@ -4343,7 +4343,7 @@
       <x:c r="U163" s="12" t="str"/>
       <x:c r="V163" s="12" t="str"/>
     </x:row>
-    <x:row r="164" ht="20" customHeight="1">
+    <x:row r="164">
       <x:c r="A164" s="12" t="str"/>
       <x:c r="B164" s="12" t="str"/>
       <x:c r="C164" s="14" t="str"/>
@@ -4367,7 +4367,7 @@
       <x:c r="U164" s="12" t="str"/>
       <x:c r="V164" s="12" t="str"/>
     </x:row>
-    <x:row r="165" ht="20" customHeight="1">
+    <x:row r="165">
       <x:c r="A165" s="12" t="str"/>
       <x:c r="B165" s="12" t="str"/>
       <x:c r="C165" s="14" t="str"/>
@@ -4391,7 +4391,7 @@
       <x:c r="U165" s="12" t="str"/>
       <x:c r="V165" s="12" t="str"/>
     </x:row>
-    <x:row r="166" ht="20" customHeight="1">
+    <x:row r="166">
       <x:c r="A166" s="12" t="str"/>
       <x:c r="B166" s="12" t="str"/>
       <x:c r="C166" s="14" t="str"/>
@@ -4415,7 +4415,7 @@
       <x:c r="U166" s="12" t="str"/>
       <x:c r="V166" s="12" t="str"/>
     </x:row>
-    <x:row r="167" ht="20" customHeight="1">
+    <x:row r="167">
       <x:c r="A167" s="12" t="str"/>
       <x:c r="B167" s="12" t="str"/>
       <x:c r="C167" s="14" t="str"/>
@@ -4439,7 +4439,7 @@
       <x:c r="U167" s="12" t="str"/>
       <x:c r="V167" s="12" t="str"/>
     </x:row>
-    <x:row r="168" ht="20" customHeight="1">
+    <x:row r="168">
       <x:c r="A168" s="12" t="str"/>
       <x:c r="B168" s="12" t="str"/>
       <x:c r="C168" s="14" t="str"/>
@@ -4463,7 +4463,7 @@
       <x:c r="U168" s="12" t="str"/>
       <x:c r="V168" s="12" t="str"/>
     </x:row>
-    <x:row r="169" ht="20" customHeight="1">
+    <x:row r="169">
       <x:c r="A169" s="12" t="str"/>
       <x:c r="B169" s="12" t="str"/>
       <x:c r="C169" s="14" t="str"/>
@@ -4487,7 +4487,7 @@
       <x:c r="U169" s="12" t="str"/>
       <x:c r="V169" s="12" t="str"/>
     </x:row>
-    <x:row r="170" ht="20" customHeight="1">
+    <x:row r="170">
       <x:c r="A170" s="12" t="str"/>
       <x:c r="B170" s="12" t="str"/>
       <x:c r="C170" s="14" t="str"/>
@@ -4511,7 +4511,7 @@
       <x:c r="U170" s="12" t="str"/>
       <x:c r="V170" s="12" t="str"/>
     </x:row>
-    <x:row r="171" ht="20" customHeight="1">
+    <x:row r="171">
       <x:c r="A171" s="12" t="str"/>
       <x:c r="B171" s="12" t="str"/>
       <x:c r="C171" s="14" t="str"/>
@@ -4535,7 +4535,7 @@
       <x:c r="U171" s="12" t="str"/>
       <x:c r="V171" s="12" t="str"/>
     </x:row>
-    <x:row r="172" ht="20" customHeight="1">
+    <x:row r="172">
       <x:c r="A172" s="12" t="str"/>
       <x:c r="B172" s="12" t="str"/>
       <x:c r="C172" s="14" t="str"/>
@@ -4559,7 +4559,7 @@
       <x:c r="U172" s="12" t="str"/>
       <x:c r="V172" s="12" t="str"/>
     </x:row>
-    <x:row r="173" ht="20" customHeight="1">
+    <x:row r="173">
       <x:c r="A173" s="12" t="str"/>
       <x:c r="B173" s="12" t="str"/>
       <x:c r="C173" s="14" t="str"/>
@@ -4583,7 +4583,7 @@
       <x:c r="U173" s="12" t="str"/>
       <x:c r="V173" s="12" t="str"/>
     </x:row>
-    <x:row r="174" ht="20" customHeight="1">
+    <x:row r="174">
       <x:c r="A174" s="12" t="str"/>
       <x:c r="B174" s="12" t="str"/>
       <x:c r="C174" s="14" t="str"/>
@@ -4607,7 +4607,7 @@
       <x:c r="U174" s="12" t="str"/>
       <x:c r="V174" s="12" t="str"/>
     </x:row>
-    <x:row r="175" ht="20" customHeight="1">
+    <x:row r="175">
       <x:c r="A175" s="12" t="str"/>
       <x:c r="B175" s="12" t="str"/>
       <x:c r="C175" s="14" t="str"/>
@@ -4631,7 +4631,7 @@
       <x:c r="U175" s="12" t="str"/>
       <x:c r="V175" s="12" t="str"/>
     </x:row>
-    <x:row r="176" ht="20" customHeight="1">
+    <x:row r="176">
       <x:c r="A176" s="12" t="str"/>
       <x:c r="B176" s="12" t="str"/>
       <x:c r="C176" s="14" t="str"/>
@@ -4655,7 +4655,7 @@
       <x:c r="U176" s="12" t="str"/>
       <x:c r="V176" s="12" t="str"/>
     </x:row>
-    <x:row r="177" ht="20" customHeight="1">
+    <x:row r="177">
       <x:c r="A177" s="12" t="str"/>
       <x:c r="B177" s="12" t="str"/>
       <x:c r="C177" s="14" t="str"/>
@@ -4679,7 +4679,7 @@
       <x:c r="U177" s="12" t="str"/>
       <x:c r="V177" s="12" t="str"/>
     </x:row>
-    <x:row r="178" ht="20" customHeight="1">
+    <x:row r="178">
       <x:c r="A178" s="12" t="str"/>
       <x:c r="B178" s="12" t="str"/>
       <x:c r="C178" s="14" t="str"/>
@@ -4703,7 +4703,7 @@
       <x:c r="U178" s="12" t="str"/>
       <x:c r="V178" s="12" t="str"/>
     </x:row>
-    <x:row r="179" ht="20" customHeight="1">
+    <x:row r="179">
       <x:c r="A179" s="12" t="str"/>
       <x:c r="B179" s="12" t="str"/>
       <x:c r="C179" s="14" t="str"/>
@@ -4727,7 +4727,7 @@
       <x:c r="U179" s="12" t="str"/>
       <x:c r="V179" s="12" t="str"/>
     </x:row>
-    <x:row r="180" ht="20" customHeight="1">
+    <x:row r="180">
       <x:c r="A180" s="12" t="str"/>
       <x:c r="B180" s="12" t="str"/>
       <x:c r="C180" s="14" t="str"/>
@@ -4751,7 +4751,7 @@
       <x:c r="U180" s="12" t="str"/>
       <x:c r="V180" s="12" t="str"/>
     </x:row>
-    <x:row r="181" ht="20" customHeight="1">
+    <x:row r="181">
       <x:c r="A181" s="12" t="str"/>
       <x:c r="B181" s="12" t="str"/>
       <x:c r="C181" s="14" t="str"/>
@@ -4775,7 +4775,7 @@
       <x:c r="U181" s="12" t="str"/>
       <x:c r="V181" s="12" t="str"/>
     </x:row>
-    <x:row r="182" ht="20" customHeight="1">
+    <x:row r="182">
       <x:c r="A182" s="12" t="str"/>
       <x:c r="B182" s="12" t="str"/>
       <x:c r="C182" s="14" t="str"/>
@@ -4799,7 +4799,7 @@
       <x:c r="U182" s="12" t="str"/>
       <x:c r="V182" s="12" t="str"/>
     </x:row>
-    <x:row r="183" ht="20" customHeight="1">
+    <x:row r="183">
       <x:c r="A183" s="12" t="str"/>
       <x:c r="B183" s="12" t="str"/>
       <x:c r="C183" s="14" t="str"/>
@@ -4823,7 +4823,7 @@
       <x:c r="U183" s="12" t="str"/>
       <x:c r="V183" s="12" t="str"/>
     </x:row>
-    <x:row r="184" ht="20" customHeight="1">
+    <x:row r="184">
       <x:c r="A184" s="12" t="str"/>
       <x:c r="B184" s="12" t="str"/>
       <x:c r="C184" s="14" t="str"/>
@@ -4847,7 +4847,7 @@
       <x:c r="U184" s="12" t="str"/>
       <x:c r="V184" s="12" t="str"/>
     </x:row>
-    <x:row r="185" ht="20" customHeight="1">
+    <x:row r="185">
       <x:c r="A185" s="12" t="str"/>
       <x:c r="B185" s="12" t="str"/>
       <x:c r="C185" s="14" t="str"/>
@@ -4871,7 +4871,7 @@
       <x:c r="U185" s="12" t="str"/>
       <x:c r="V185" s="12" t="str"/>
     </x:row>
-    <x:row r="186" ht="20" customHeight="1">
+    <x:row r="186">
       <x:c r="A186" s="12" t="str"/>
       <x:c r="B186" s="12" t="str"/>
       <x:c r="C186" s="14" t="str"/>
@@ -4895,7 +4895,7 @@
       <x:c r="U186" s="12" t="str"/>
       <x:c r="V186" s="12" t="str"/>
     </x:row>
-    <x:row r="187" ht="20" customHeight="1">
+    <x:row r="187">
       <x:c r="A187" s="12" t="str"/>
       <x:c r="B187" s="12" t="str"/>
       <x:c r="C187" s="14" t="str"/>
@@ -4919,7 +4919,7 @@
       <x:c r="U187" s="12" t="str"/>
       <x:c r="V187" s="12" t="str"/>
     </x:row>
-    <x:row r="188" ht="20" customHeight="1">
+    <x:row r="188">
       <x:c r="A188" s="12" t="str"/>
       <x:c r="B188" s="12" t="str"/>
       <x:c r="C188" s="14" t="str"/>
@@ -4943,7 +4943,7 @@
       <x:c r="U188" s="12" t="str"/>
       <x:c r="V188" s="12" t="str"/>
     </x:row>
-    <x:row r="189" ht="20" customHeight="1">
+    <x:row r="189">
       <x:c r="A189" s="12" t="str"/>
       <x:c r="B189" s="12" t="str"/>
       <x:c r="C189" s="14" t="str"/>
@@ -4967,7 +4967,7 @@
       <x:c r="U189" s="12" t="str"/>
       <x:c r="V189" s="12" t="str"/>
     </x:row>
-    <x:row r="190" ht="20" customHeight="1">
+    <x:row r="190">
       <x:c r="A190" s="12" t="str"/>
       <x:c r="B190" s="12" t="str"/>
       <x:c r="C190" s="14" t="str"/>
@@ -4991,7 +4991,7 @@
       <x:c r="U190" s="12" t="str"/>
       <x:c r="V190" s="12" t="str"/>
     </x:row>
-    <x:row r="191" ht="20" customHeight="1">
+    <x:row r="191">
       <x:c r="A191" s="12" t="str"/>
       <x:c r="B191" s="12" t="str"/>
       <x:c r="C191" s="14" t="str"/>
@@ -5015,7 +5015,7 @@
       <x:c r="U191" s="12" t="str"/>
       <x:c r="V191" s="12" t="str"/>
     </x:row>
-    <x:row r="192" ht="20" customHeight="1">
+    <x:row r="192">
       <x:c r="A192" s="12" t="str"/>
       <x:c r="B192" s="12" t="str"/>
       <x:c r="C192" s="14" t="str"/>
@@ -5039,7 +5039,7 @@
       <x:c r="U192" s="12" t="str"/>
       <x:c r="V192" s="12" t="str"/>
     </x:row>
-    <x:row r="193" ht="20" customHeight="1">
+    <x:row r="193">
       <x:c r="A193" s="12" t="str"/>
       <x:c r="B193" s="12" t="str"/>
       <x:c r="C193" s="14" t="str"/>
@@ -5063,7 +5063,7 @@
       <x:c r="U193" s="12" t="str"/>
       <x:c r="V193" s="12" t="str"/>
     </x:row>
-    <x:row r="194" ht="20" customHeight="1">
+    <x:row r="194">
       <x:c r="A194" s="12" t="str"/>
       <x:c r="B194" s="12" t="str"/>
       <x:c r="C194" s="14" t="str"/>
@@ -5087,7 +5087,7 @@
       <x:c r="U194" s="12" t="str"/>
       <x:c r="V194" s="12" t="str"/>
     </x:row>
-    <x:row r="195" ht="20" customHeight="1">
+    <x:row r="195">
       <x:c r="A195" s="12" t="str"/>
       <x:c r="B195" s="12" t="str"/>
       <x:c r="C195" s="14" t="str"/>
@@ -5111,7 +5111,7 @@
       <x:c r="U195" s="12" t="str"/>
       <x:c r="V195" s="12" t="str"/>
     </x:row>
-    <x:row r="196" ht="20" customHeight="1">
+    <x:row r="196">
       <x:c r="A196" s="12" t="str"/>
       <x:c r="B196" s="12" t="str"/>
       <x:c r="C196" s="14" t="str"/>
@@ -5135,7 +5135,7 @@
       <x:c r="U196" s="12" t="str"/>
       <x:c r="V196" s="12" t="str"/>
     </x:row>
-    <x:row r="197" ht="20" customHeight="1">
+    <x:row r="197">
       <x:c r="A197" s="12" t="str"/>
       <x:c r="B197" s="12" t="str"/>
       <x:c r="C197" s="14" t="str"/>
@@ -5159,7 +5159,7 @@
       <x:c r="U197" s="12" t="str"/>
       <x:c r="V197" s="12" t="str"/>
     </x:row>
-    <x:row r="198" ht="20" customHeight="1">
+    <x:row r="198">
       <x:c r="A198" s="12" t="str"/>
       <x:c r="B198" s="12" t="str"/>
       <x:c r="C198" s="14" t="str"/>
@@ -5183,7 +5183,7 @@
       <x:c r="U198" s="12" t="str"/>
       <x:c r="V198" s="12" t="str"/>
     </x:row>
-    <x:row r="199" ht="20" customHeight="1">
+    <x:row r="199">
       <x:c r="A199" s="12" t="str"/>
       <x:c r="B199" s="12" t="str"/>
       <x:c r="C199" s="14" t="str"/>
@@ -5207,7 +5207,7 @@
       <x:c r="U199" s="12" t="str"/>
       <x:c r="V199" s="12" t="str"/>
     </x:row>
-    <x:row r="200" ht="20" customHeight="1">
+    <x:row r="200">
       <x:c r="A200" s="12" t="str"/>
       <x:c r="B200" s="12" t="str"/>
       <x:c r="C200" s="14" t="str"/>
@@ -5231,7 +5231,7 @@
       <x:c r="U200" s="12" t="str"/>
       <x:c r="V200" s="12" t="str"/>
     </x:row>
-    <x:row r="201" ht="20" customHeight="1">
+    <x:row r="201">
       <x:c r="A201" s="12" t="str"/>
       <x:c r="B201" s="12" t="str"/>
       <x:c r="C201" s="14" t="str"/>
@@ -5481,12 +5481,54 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="C4" s="26"/>
-      <x:c r="E4" s="26"/>
-      <x:c r="G4" s="26"/>
-      <x:c r="N4" s="26"/>
-      <x:c r="Q4" s="26"/>
-      <x:c r="T4" s="26"/>
+      <x:c r="A4" s="12" t="str">
+        <x:v>PESSOA FÍSICA EXEMPLO</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str"/>
+      <x:c r="C4" s="14" t="str">
+        <x:v>123.456.789-01</x:v>
+      </x:c>
+      <x:c r="D4" s="12" t="str">
+        <x:v>pessoa@example.com</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>89200-000</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="str">
+        <x:v>RUA EXEMPLO</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H4" s="12" t="str"/>
+      <x:c r="I4" s="12" t="str">
+        <x:v>CENTRO</x:v>
+      </x:c>
+      <x:c r="J4" s="12" t="str">
+        <x:v>JOINVILLE</x:v>
+      </x:c>
+      <x:c r="K4" s="12" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="L4" s="12" t="str">
+        <x:v>PESSOA EXEMPLO</x:v>
+      </x:c>
+      <x:c r="M4" s="12" t="str"/>
+      <x:c r="N4" s="14" t="str">
+        <x:v>(47) 99999-9999</x:v>
+      </x:c>
+      <x:c r="O4" s="12" t="str"/>
+      <x:c r="P4" s="12" t="str"/>
+      <x:c r="Q4" s="14" t="str"/>
+      <x:c r="R4" s="12" t="str"/>
+      <x:c r="S4" s="12" t="str"/>
+      <x:c r="T4" s="14" t="str"/>
+      <x:c r="U4" s="12" t="str">
+        <x:v>EXEMPLO COM CPF — ESTA LINHA SERÁ IGNORADA AUTOMATICAMENTE.</x:v>
+      </x:c>
+      <x:c r="V4" s="12" t="str">
+        <x:v>SIM</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="C5" s="26"/>
@@ -6265,8 +6307,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="78" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="84" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -6279,7 +6321,7 @@
       <x:c r="E1" s="31"/>
       <x:c r="F1" s="31"/>
     </x:row>
-    <x:row r="3" ht="34" customHeight="1">
+    <x:row r="3" ht="36" customHeight="1">
       <x:c r="A3" s="40" t="str">
         <x:v>Regra</x:v>
       </x:c>
@@ -6287,7 +6329,7 @@
         <x:v>Orientação</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="34" customHeight="1">
+    <x:row r="4" ht="36" customHeight="1">
       <x:c r="A4" s="12" t="str">
         <x:v>Aba a preencher</x:v>
       </x:c>
@@ -6295,83 +6337,91 @@
         <x:v>Use somente a aba IMPORTAR_CLIENTES para a importação.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="34" customHeight="1">
+    <x:row r="5" ht="36" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>Campos obrigatórios</x:v>
+        <x:v>Pessoas físicas / CPF</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
+        <x:v>NÃO serão importadas. Se a coluna CNPJ contiver um documento com 11 dígitos (CPF), a linha será marcada como IGNORADO CPF e não bloqueará o restante da importação.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="12" t="str">
+        <x:v>Campos obrigatórios para CNPJ</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="str">
         <x:v>Razão Social, CNPJ, Logradouro, Número, Bairro, Cidade, UF, Contato Principal Nome e Contato Principal Telefone/WhatsApp.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="12" t="str">
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="12" t="str">
         <x:v>CNPJ</x:v>
       </x:c>
-      <x:c r="B6" s="12" t="str">
-        <x:v>Mantenha o CNPJ como texto. Pontuação é aceita. O sistema compara o CNPJ normalizado para impedir duplicidades.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="34" customHeight="1">
-      <x:c r="A7" s="12" t="str">
+      <x:c r="B7" s="12" t="str">
+        <x:v>Mantenha o CNPJ como texto. Pontuação é aceita. O sistema usa os 14 dígitos para impedir duplicidades.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="12" t="str">
         <x:v>Contato principal</x:v>
       </x:c>
-      <x:c r="B7" s="12" t="str">
+      <x:c r="B8" s="12" t="str">
         <x:v>É o contato usado automaticamente no Suporte OSR e como telefone/WhatsApp principal no App do Técnico.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="34" customHeight="1">
-      <x:c r="A8" s="12" t="str">
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="12" t="str">
         <x:v>Endereço</x:v>
       </x:c>
-      <x:c r="B8" s="12" t="str">
+      <x:c r="B9" s="12" t="str">
         <x:v>O sistema monta um Endereço Completo com Logradouro, Número, Complemento, Bairro, Cidade, UF e CEP.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="12" t="str">
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="12" t="str">
         <x:v>Contatos adicionais</x:v>
       </x:c>
-      <x:c r="B9" s="12" t="str">
+      <x:c r="B10" s="12" t="str">
         <x:v>Contato 2 e Contato 3 são opcionais.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="34" customHeight="1">
-      <x:c r="A10" s="12" t="str">
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="12" t="str">
         <x:v>Ativo</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="str">
+      <x:c r="B11" s="12" t="str">
         <x:v>Use SIM ou NÃO. Se ficar em branco, o sistema considera o cliente ativo.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="34" customHeight="1">
-      <x:c r="A11" s="12" t="str">
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" s="12" t="str">
         <x:v>Duplicidades</x:v>
       </x:c>
-      <x:c r="B11" s="12" t="str">
+      <x:c r="B12" s="12" t="str">
         <x:v>A importação analisa duplicidades dentro da planilha e no banco antes de liberar o botão Importar.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="34" customHeight="1">
-      <x:c r="A12" s="12" t="str">
+    <x:row r="13" ht="36" customHeight="1">
+      <x:c r="A13" s="12" t="str">
         <x:v>Cliente já existente</x:v>
       </x:c>
-      <x:c r="B12" s="12" t="str">
+      <x:c r="B13" s="12" t="str">
         <x:v>Se houver exatamente um cliente com o mesmo CNPJ, o sistema atualiza o cadastro em vez de criar outro.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="34" customHeight="1">
-      <x:c r="A13" s="12" t="str">
+    <x:row r="14" ht="36" customHeight="1">
+      <x:c r="A14" s="12" t="str">
         <x:v>Cliente removido</x:v>
       </x:c>
-      <x:c r="B13" s="12" t="str">
+      <x:c r="B14" s="12" t="str">
         <x:v>Se o mesmo cliente estiver removido logicamente, a importação reativa o mesmo ID, preservando vínculos históricos.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="34" customHeight="1">
-      <x:c r="A14" s="12" t="str">
+    <x:row r="15" ht="36" customHeight="1">
+      <x:c r="A15" s="12" t="str">
         <x:v>Exemplo</x:v>
       </x:c>
-      <x:c r="B14" s="12" t="str">
+      <x:c r="B15" s="12" t="str">
         <x:v>Consulte a aba EXEMPLO_PREENCHIDO. Os dados são fictícios e não devem ser importados.</x:v>
       </x:c>
     </x:row>
